--- a/Mapping_Anlagekriterien.xlsx
+++ b/Mapping_Anlagekriterien.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -989,6 +989,117 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Offensiv</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Thema</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Offensiv</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Weltweit</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mind. 50 %, max. 100 %</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>max. 50 %</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Unbegrenzt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thema</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Weltweit</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>max. 100 %</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>max. 15 %</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Unbegrenzt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pro Dividende</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Thema</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pro Dividende</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Weltweit</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>max. 100 %</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>max. 15 %</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Unbegrenzt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
